--- a/Data/EC/NIT-9013893581.xlsx
+++ b/Data/EC/NIT-9013893581.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CF4DBA4-3FA1-4A0F-BBD3-0EB7AC850968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1ABCA85-9FA3-471D-B00C-AE5E88D027F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{2F700F6C-7879-43BA-A7AD-0672B947C739}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{60F22B29-3D31-49E1-8EFC-3DF184D30182}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>LUIS ALFONSO PEREZ GARCIA</t>
+  </si>
+  <si>
+    <t>2607</t>
   </si>
   <si>
     <t>2606</t>
@@ -569,22 +572,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31FF022C-7203-7D4D-CE4B-D986BFDA8736}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9766C5E1-689A-3059-0D6F-C1D1EEB8F43D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -593,7 +596,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -606,7 +609,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -935,27 +938,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5A79F9-31F0-4783-95F8-FB6A3360E55A}">
-  <dimension ref="B2:J48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBFCC576-8441-4060-8FA0-FD139782262A}">
+  <dimension ref="B2:J49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.06640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -964,7 +967,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -975,7 +978,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -986,7 +989,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -997,10 +1000,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1013,8 +1016,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1029,15 +1032,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>1924682</v>
+        <v>2004682</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1045,27 +1048,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5">
         <v>4</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1085,16 +1088,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="J15" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1117,7 +1120,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1140,7 +1143,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1163,7 +1166,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1186,7 +1189,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1209,7 +1212,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1232,7 +1235,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1255,7 +1258,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1278,7 +1281,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1301,7 +1304,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1324,7 +1327,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1347,7 +1350,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1370,7 +1373,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1393,7 +1396,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1416,7 +1419,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1439,7 +1442,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1462,7 +1465,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1485,7 +1488,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1508,7 +1511,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1522,7 +1525,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>48000</v>
+        <v>80000</v>
       </c>
       <c r="G34" s="18">
         <v>2000000</v>
@@ -1531,44 +1534,44 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>32</v>
-      </c>
       <c r="F35" s="18">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="G35" s="18">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F36" s="18">
-        <v>84000</v>
+        <v>40000</v>
       </c>
       <c r="G36" s="18">
         <v>1000000</v>
@@ -1577,15 +1580,15 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>34</v>
@@ -1600,38 +1603,38 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>37</v>
-      </c>
       <c r="F38" s="18">
-        <v>36341</v>
+        <v>84000</v>
       </c>
       <c r="G38" s="18">
-        <v>908526</v>
+        <v>1000000</v>
       </c>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E39" s="16" t="s">
         <v>38</v>
@@ -1646,38 +1649,38 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>41</v>
-      </c>
       <c r="F40" s="18">
-        <v>52000</v>
+        <v>36341</v>
       </c>
       <c r="G40" s="18">
-        <v>1300000</v>
+        <v>908526</v>
       </c>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>42</v>
@@ -1692,43 +1695,55 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B42" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="23" t="s">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E42" s="22" t="s">
+      <c r="D42" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="18">
         <v>52000</v>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="18">
         <v>1300000</v>
       </c>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="26"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B47" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="32"/>
-      <c r="H47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="24">
+        <v>52000</v>
+      </c>
+      <c r="G43" s="24">
+        <v>1300000</v>
+      </c>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="26"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C48" s="32"/>
       <c r="H48" s="1" t="s">
@@ -1737,12 +1752,23 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="32"/>
+      <c r="H49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="H49:J49"/>
     <mergeCell ref="H48:J48"/>
-    <mergeCell ref="H47:J47"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
